--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -675,57 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129680287</v>
+        <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>105822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gisselåsen, Söderåsen, Selånger, Mpd</t>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608812</v>
+        <v>608716</v>
       </c>
       <c r="R2" t="n">
-        <v>6919133</v>
+        <v>6919160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129677106</v>
+        <v>129675462</v>
       </c>
       <c r="B3" t="n">
-        <v>105822</v>
+        <v>56911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608716</v>
+        <v>609145</v>
       </c>
       <c r="R3" t="n">
-        <v>6919160</v>
+        <v>6919165</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129675462</v>
+        <v>129680287</v>
       </c>
       <c r="B4" t="n">
-        <v>56911</v>
+        <v>57731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -910,16 +898,28 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
+          <t>Gisselåsen, Söderåsen, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609145</v>
+        <v>608812</v>
       </c>
       <c r="R4" t="n">
-        <v>6919165</v>
+        <v>6919133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129675462</v>
       </c>
       <c r="B3" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129680287</v>
       </c>
       <c r="B4" t="n">
-        <v>57731</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129675462</v>
       </c>
       <c r="B3" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129680287</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129680287</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129677106</v>
       </c>
       <c r="B2" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129675462</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129677106</v>
+        <v>129676978</v>
       </c>
       <c r="B2" t="n">
-        <v>105881</v>
+        <v>89033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4395</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lädervaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cuphophyllus russocoriaceus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Berk. &amp; Jos.K.Miller) Bon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608716</v>
+        <v>608755</v>
       </c>
       <c r="R2" t="n">
-        <v>6919160</v>
+        <v>6919114</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129675462</v>
+        <v>129677063</v>
       </c>
       <c r="B3" t="n">
-        <v>56921</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609145</v>
+        <v>608747</v>
       </c>
       <c r="R3" t="n">
-        <v>6919165</v>
+        <v>6919181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129680287</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,6 +975,685 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129675462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergmanstorpet, Västeråsen  Selånger, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>609145</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6919165</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129675371</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>609172</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6919144</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129675720</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergmanstorpet, Bergmanstorpet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>609174</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6919130</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129676730</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608827</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6919124</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129677052</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608761</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6919168</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129677092</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608742</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6919174</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129677106</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högmyrbäcken, Högmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>608716</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6919160</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47129-2025 artfynd.xlsx
+++ b/artfynd/A 47129-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129676978</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129677063</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129680287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129677052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129677092</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129677106</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675462</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675371</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675720</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,8 +1704,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129676730</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>